--- a/tests/SafeOpenXml.Tests/Examples/Image/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0d4be834b79c4400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3901a7c4037e4bf6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R9915e602f0344035"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2f1116fcb9e74475"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19f365f7beef47f2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe801c15b9f946a2"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Image/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3901a7c4037e4bf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R68de924d7ea94d8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2f1116fcb9e74475"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf52487712bb449f5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe801c15b9f946a2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9239a27d6654c39"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Image/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Image/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R68de924d7ea94d8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R546eef0980ea4e19"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf52487712bb449f5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd9c7fb952f704673"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -93,6 +93,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9239a27d6654c39"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c3e3700242141a4"/>
 </x:worksheet>
 </file>